--- a/results/06_model_evaluation_nested/05_ALL_model_eval.xlsx
+++ b/results/06_model_evaluation_nested/05_ALL_model_eval.xlsx
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7416451769600094</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01993688661995984</v>
+        <v>0.02055176014088759</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1154322800342247</v>
+        <v>0.113979645704231</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01432159611287153</v>
+        <v>0.01327209032282319</v>
       </c>
     </row>
     <row r="7">
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.778291616922111</v>
+        <v>0.7638655851081998</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02016460778089968</v>
+        <v>0.01830461526364529</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1366611393084907</v>
+        <v>0.1305084174604524</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01644375607216518</v>
+        <v>0.01322728173796852</v>
       </c>
     </row>
     <row r="8">
@@ -622,16 +622,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.740204074741885</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01632377788364275</v>
+        <v>0.01740707860779314</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1504672166943709</v>
+        <v>0.150418939148557</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01174477485781384</v>
+        <v>0.01096860461154251</v>
       </c>
     </row>
     <row r="9">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00960631081931577</v>
+        <v>0.008404306776686604</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2179801169523388</v>
+        <v>0.2163882894451978</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01386992304711891</v>
+        <v>0.01225359127876926</v>
       </c>
     </row>
     <row r="10">
@@ -670,16 +670,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8380082807867801</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02096671842468235</v>
+        <v>0.02144293790929938</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3626783404222963</v>
+        <v>0.3621556760174849</v>
       </c>
       <c r="F10" t="n">
-        <v>0.036706105017073</v>
+        <v>0.03892340905464424</v>
       </c>
     </row>
     <row r="11">
@@ -694,16 +694,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="D11" t="n">
-        <v>0.007267449988741658</v>
+        <v>0.008279770287604037</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4197146136049616</v>
+        <v>0.4183159022170709</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05043702845977172</v>
+        <v>0.05664601097712555</v>
       </c>
     </row>
     <row r="12">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7416451769600094</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01993688661995984</v>
+        <v>0.02055176014088759</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1154322800342247</v>
+        <v>0.113979645704231</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01432159611287153</v>
+        <v>0.01327209032282319</v>
       </c>
     </row>
     <row r="23">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7753054223485613</v>
+        <v>0.7645097964865715</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01970127916584561</v>
+        <v>0.01998253139500118</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1352904023718657</v>
+        <v>0.1256960788106765</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01580335909372842</v>
+        <v>0.0111111875630107</v>
       </c>
     </row>
     <row r="24">
@@ -1006,16 +1006,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7706431402325833</v>
+        <v>0.7675390063081083</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01824097132401747</v>
+        <v>0.01865128568652915</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1348461163055937</v>
+        <v>0.1342371441199022</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01796663639692724</v>
+        <v>0.01543301317163794</v>
       </c>
     </row>
     <row r="25">
@@ -1030,16 +1030,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7602130881745923</v>
+        <v>0.7544951316937933</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01392039267849403</v>
+        <v>0.01135738628816723</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1381007774329141</v>
+        <v>0.1182847363702429</v>
       </c>
       <c r="F25" t="n">
-        <v>0.006304980123472345</v>
+        <v>0.00858114579579135</v>
       </c>
     </row>
     <row r="26">
@@ -1054,16 +1054,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7683861628742591</v>
+        <v>0.7643554917214723</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01822216654225288</v>
+        <v>0.01846287389594341</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1372334173685621</v>
+        <v>0.1308379294871899</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01279874061212412</v>
+        <v>0.01051598906289089</v>
       </c>
     </row>
     <row r="27">
@@ -1078,16 +1078,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.740204074741885</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01632377788364275</v>
+        <v>0.01740707860779314</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1504672166943709</v>
+        <v>0.150418939148557</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01174477485781384</v>
+        <v>0.01096860461154251</v>
       </c>
     </row>
     <row r="28">
@@ -1102,16 +1102,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.7871773576552643</v>
+        <v>0.7883998687445136</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01052812384353352</v>
+        <v>0.008023982756139258</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1973119681773526</v>
+        <v>0.1983542113814164</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0126853747689661</v>
+        <v>0.02016621122068829</v>
       </c>
     </row>
     <row r="29">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.7735862526102607</v>
+        <v>0.7753354867186564</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01355371744243104</v>
+        <v>0.01269043437239893</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1759112725474974</v>
+        <v>0.17448342405062</v>
       </c>
       <c r="F29" t="n">
-        <v>0.009687400006006397</v>
+        <v>0.01082047555388005</v>
       </c>
     </row>
     <row r="30">
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.7524403559136705</v>
+        <v>0.7519759936135035</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01815809526707301</v>
+        <v>0.01897235505529942</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1561432319098676</v>
+        <v>0.1604473928142211</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02485627758998294</v>
+        <v>0.02469004502687826</v>
       </c>
     </row>
     <row r="31">
@@ -1174,16 +1174,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.7729417717062963</v>
+        <v>0.774307977615377</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01696652667544666</v>
+        <v>0.01587442623235423</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1942662352121397</v>
+        <v>0.1950261679377055</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01901994907284056</v>
+        <v>0.01799920717845304</v>
       </c>
     </row>
     <row r="32">
@@ -1198,16 +1198,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.8380082807867801</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02096671842468235</v>
+        <v>0.02144293790929938</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3626783404222963</v>
+        <v>0.3621556760174849</v>
       </c>
       <c r="F32" t="n">
-        <v>0.036706105017073</v>
+        <v>0.03892340905464424</v>
       </c>
     </row>
     <row r="33">
@@ -1222,16 +1222,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.8574353556750157</v>
+        <v>0.8560991058465504</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01799383944150814</v>
+        <v>0.01482657545051336</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3886767546878503</v>
+        <v>0.39299150315043</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03992927212471939</v>
+        <v>0.04328364565501456</v>
       </c>
     </row>
     <row r="34">
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.8565860138008118</v>
+        <v>0.8581412102778174</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01338845306581416</v>
+        <v>0.01343351241384613</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3853073807126989</v>
+        <v>0.3894527575943291</v>
       </c>
       <c r="F34" t="n">
-        <v>0.04225413424787459</v>
+        <v>0.04159488439462301</v>
       </c>
     </row>
     <row r="35">
@@ -1270,16 +1270,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.8352441775362471</v>
+        <v>0.8341393621732202</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0196280256658652</v>
+        <v>0.0194148298495687</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2894366220528332</v>
+        <v>0.28501264267978</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02287044597953614</v>
+        <v>0.02798555356943055</v>
       </c>
     </row>
     <row r="36">
@@ -1294,16 +1294,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.8583037287540549</v>
+        <v>0.859008083773802</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01749714474713204</v>
+        <v>0.01775204446314711</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3999103855990315</v>
+        <v>0.4019031011699147</v>
       </c>
       <c r="F36" t="n">
-        <v>0.04408977752764391</v>
+        <v>0.05002623507853219</v>
       </c>
     </row>
   </sheetData>
@@ -1408,20 +1408,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>extratrees</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.778291616922111</v>
+        <v>0.7675390063081083</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02016460778089968</v>
+        <v>0.01865128568652915</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1366611393084907</v>
+        <v>0.1342371441199022</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01644375607216518</v>
+        <v>0.01543301317163794</v>
       </c>
     </row>
     <row r="5">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00960631081931577</v>
+        <v>0.008404306776686604</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2179801169523388</v>
+        <v>0.2163882894451978</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01386992304711891</v>
+        <v>0.01225359127876926</v>
       </c>
     </row>
     <row r="6">
@@ -1460,16 +1460,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007267449988741658</v>
+        <v>0.008279770287604037</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4197146136049616</v>
+        <v>0.4183159022170709</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05043702845977172</v>
+        <v>0.05664601097712555</v>
       </c>
     </row>
   </sheetData>
@@ -1868,16 +1868,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7416451769600094</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01993688661995984</v>
+        <v>0.02055176014088759</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1154322800342247</v>
+        <v>0.113979645704231</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01432159611287153</v>
+        <v>0.01327209032282319</v>
       </c>
     </row>
     <row r="3">
@@ -1887,16 +1887,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.778291616922111</v>
+        <v>0.7638655851081998</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02016460778089968</v>
+        <v>0.01830461526364529</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1366611393084907</v>
+        <v>0.1305084174604524</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01644375607216518</v>
+        <v>0.01322728173796852</v>
       </c>
     </row>
     <row r="4">
@@ -1906,16 +1906,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7416451769600094</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01993688661995984</v>
+        <v>0.02055176014088759</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1154322800342247</v>
+        <v>0.113979645704231</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01432159611287153</v>
+        <v>0.01327209032282319</v>
       </c>
     </row>
     <row r="5">
@@ -1925,16 +1925,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7753054223485613</v>
+        <v>0.7645097964865715</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01970127916584561</v>
+        <v>0.01998253139500118</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1352904023718657</v>
+        <v>0.1256960788106765</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01580335909372842</v>
+        <v>0.0111111875630107</v>
       </c>
     </row>
     <row r="6">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7706431402325833</v>
+        <v>0.7675390063081083</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01824097132401747</v>
+        <v>0.01865128568652915</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1348461163055937</v>
+        <v>0.1342371441199022</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01796663639692724</v>
+        <v>0.01543301317163794</v>
       </c>
     </row>
     <row r="7">
@@ -1963,16 +1963,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7602130881745923</v>
+        <v>0.7544951316937933</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01392039267849403</v>
+        <v>0.01135738628816723</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1381007774329141</v>
+        <v>0.1182847363702429</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006304980123472345</v>
+        <v>0.00858114579579135</v>
       </c>
     </row>
     <row r="8">
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7683861628742591</v>
+        <v>0.7643554917214723</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01822216654225288</v>
+        <v>0.01846287389594341</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1372334173685621</v>
+        <v>0.1308379294871899</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01279874061212412</v>
+        <v>0.01051598906289089</v>
       </c>
     </row>
   </sheetData>
@@ -2042,16 +2042,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.740204074741885</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01632377788364275</v>
+        <v>0.01740707860779314</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1504672166943709</v>
+        <v>0.150418939148557</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01174477485781384</v>
+        <v>0.01096860461154251</v>
       </c>
     </row>
     <row r="3">
@@ -2061,16 +2061,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00960631081931577</v>
+        <v>0.008404306776686604</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2179801169523388</v>
+        <v>0.2163882894451978</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01386992304711891</v>
+        <v>0.01225359127876926</v>
       </c>
     </row>
     <row r="4">
@@ -2080,16 +2080,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.740204074741885</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01632377788364275</v>
+        <v>0.01740707860779314</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1504672166943709</v>
+        <v>0.150418939148557</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01174477485781384</v>
+        <v>0.01096860461154251</v>
       </c>
     </row>
     <row r="5">
@@ -2099,16 +2099,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7871773576552643</v>
+        <v>0.7883998687445136</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01052812384353352</v>
+        <v>0.008023982756139258</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1973119681773526</v>
+        <v>0.1983542113814164</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0126853747689661</v>
+        <v>0.02016621122068829</v>
       </c>
     </row>
     <row r="6">
@@ -2118,16 +2118,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7735862526102607</v>
+        <v>0.7753354867186564</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01355371744243104</v>
+        <v>0.01269043437239893</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1759112725474974</v>
+        <v>0.17448342405062</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009687400006006397</v>
+        <v>0.01082047555388005</v>
       </c>
     </row>
     <row r="7">
@@ -2137,16 +2137,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7524403559136705</v>
+        <v>0.7519759936135035</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01815809526707301</v>
+        <v>0.01897235505529942</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1561432319098676</v>
+        <v>0.1604473928142211</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02485627758998294</v>
+        <v>0.02469004502687826</v>
       </c>
     </row>
     <row r="8">
@@ -2156,16 +2156,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7729417717062963</v>
+        <v>0.774307977615377</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01696652667544666</v>
+        <v>0.01587442623235423</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1942662352121397</v>
+        <v>0.1950261679377055</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01901994907284056</v>
+        <v>0.01799920717845304</v>
       </c>
     </row>
   </sheetData>
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8380082807867801</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02096671842468235</v>
+        <v>0.02144293790929938</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3626783404222963</v>
+        <v>0.3621556760174849</v>
       </c>
       <c r="E2" t="n">
-        <v>0.036706105017073</v>
+        <v>0.03892340905464424</v>
       </c>
     </row>
     <row r="3">
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007267449988741658</v>
+        <v>0.008279770287604037</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4197146136049616</v>
+        <v>0.4183159022170709</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05043702845977172</v>
+        <v>0.05664601097712555</v>
       </c>
     </row>
     <row r="4">
@@ -2254,16 +2254,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8380082807867801</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02096671842468235</v>
+        <v>0.02144293790929938</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3626783404222963</v>
+        <v>0.3621556760174849</v>
       </c>
       <c r="E4" t="n">
-        <v>0.036706105017073</v>
+        <v>0.03892340905464424</v>
       </c>
     </row>
     <row r="5">
@@ -2273,16 +2273,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8574353556750157</v>
+        <v>0.8560991058465504</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01799383944150814</v>
+        <v>0.01482657545051336</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3886767546878503</v>
+        <v>0.39299150315043</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03992927212471939</v>
+        <v>0.04328364565501456</v>
       </c>
     </row>
     <row r="6">
@@ -2292,16 +2292,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8565860138008118</v>
+        <v>0.8581412102778174</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01338845306581416</v>
+        <v>0.01343351241384613</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3853073807126989</v>
+        <v>0.3894527575943291</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04225413424787459</v>
+        <v>0.04159488439462301</v>
       </c>
     </row>
     <row r="7">
@@ -2311,16 +2311,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8352441775362471</v>
+        <v>0.8341393621732202</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0196280256658652</v>
+        <v>0.0194148298495687</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2894366220528332</v>
+        <v>0.28501264267978</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02287044597953614</v>
+        <v>0.02798555356943055</v>
       </c>
     </row>
     <row r="8">
@@ -2330,16 +2330,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8583037287540549</v>
+        <v>0.859008083773802</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01749714474713204</v>
+        <v>0.01775204446314711</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3999103855990315</v>
+        <v>0.4019031011699147</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04408977752764391</v>
+        <v>0.05002623507853219</v>
       </c>
     </row>
   </sheetData>
